--- a/output/roomself_excel/2057.xlsx
+++ b/output/roomself_excel/2057.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29106</v>
+        <v>156140</v>
       </c>
       <c r="D2" t="n">
-        <v>1372</v>
+        <v>3168</v>
       </c>
       <c r="E2" t="n">
-        <v>206</v>
+        <v>453</v>
       </c>
       <c r="F2" t="n">
-        <v>173</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>179355</v>
+        <v>201463</v>
       </c>
       <c r="D3" t="n">
-        <v>4296</v>
+        <v>4100</v>
       </c>
       <c r="E3" t="n">
-        <v>846</v>
+        <v>608</v>
       </c>
       <c r="F3" t="n">
-        <v>765</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>55919</v>
+        <v>49456</v>
       </c>
       <c r="D5" t="n">
-        <v>1920</v>
+        <v>1828</v>
       </c>
       <c r="E5" t="n">
-        <v>294</v>
+        <v>176</v>
       </c>
       <c r="F5" t="n">
-        <v>216</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28624</v>
+        <v>42431</v>
       </c>
       <c r="D6" t="n">
-        <v>1608</v>
+        <v>1728</v>
       </c>
       <c r="E6" t="n">
-        <v>230</v>
+        <v>294</v>
       </c>
       <c r="F6" t="n">
-        <v>204</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>156140</v>
+        <v>55919</v>
       </c>
       <c r="D7" t="n">
-        <v>3168</v>
+        <v>1920</v>
       </c>
       <c r="E7" t="n">
-        <v>604</v>
+        <v>294</v>
       </c>
       <c r="F7" t="n">
-        <v>453</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>397369</v>
+        <v>29106</v>
       </c>
       <c r="D8" t="n">
-        <v>9064</v>
+        <v>1372</v>
       </c>
       <c r="E8" t="n">
-        <v>853</v>
+        <v>206</v>
       </c>
       <c r="F8" t="n">
-        <v>593</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9184</v>
+        <v>179355</v>
       </c>
       <c r="D9" t="n">
-        <v>776</v>
+        <v>4296</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>846</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>36309</v>
+        <v>28624</v>
       </c>
       <c r="D10" t="n">
-        <v>1624</v>
+        <v>1608</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35112</v>
+        <v>397369</v>
       </c>
       <c r="D11" t="n">
-        <v>1528</v>
+        <v>9064</v>
       </c>
       <c r="E11" t="n">
-        <v>228</v>
+        <v>853</v>
       </c>
       <c r="F11" t="n">
-        <v>19</v>
+        <v>593</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>51704</v>
+        <v>9184</v>
       </c>
       <c r="D12" t="n">
-        <v>1860</v>
+        <v>776</v>
       </c>
       <c r="E12" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37620</v>
+        <v>36309</v>
       </c>
       <c r="D13" t="n">
-        <v>1552</v>
+        <v>1624</v>
       </c>
       <c r="E13" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>33572</v>
+        <v>35112</v>
       </c>
       <c r="D14" t="n">
-        <v>1488</v>
+        <v>1528</v>
       </c>
       <c r="E14" t="n">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="F14" t="n">
-        <v>173</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>201463</v>
+        <v>51704</v>
       </c>
       <c r="D15" t="n">
-        <v>4100</v>
+        <v>1860</v>
       </c>
       <c r="E15" t="n">
-        <v>788</v>
+        <v>184</v>
       </c>
       <c r="F15" t="n">
-        <v>398</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>49456</v>
+        <v>37620</v>
       </c>
       <c r="D16" t="n">
-        <v>1828</v>
+        <v>1552</v>
       </c>
       <c r="E16" t="n">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>42431</v>
+        <v>33572</v>
       </c>
       <c r="D17" t="n">
-        <v>1728</v>
+        <v>1488</v>
       </c>
       <c r="E17" t="n">
-        <v>294</v>
+        <v>237</v>
       </c>
       <c r="F17" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/2057.xlsx
+++ b/output/roomself_excel/2057.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,11 +510,38 @@
       <c r="D2" t="n">
         <v>3168</v>
       </c>
-      <c r="E2" t="n">
-        <v>453</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>388</v>
+        <v>370</v>
+      </c>
+      <c r="G2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>422</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>97</v>
+      </c>
+      <c r="M2" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +559,31 @@
       <c r="D3" t="n">
         <v>4100</v>
       </c>
-      <c r="E3" t="n">
-        <v>608</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>380</v>
-      </c>
+        <v>684</v>
+      </c>
+      <c r="G3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>572</v>
+      </c>
+      <c r="J3" t="n">
+        <v>18</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +600,23 @@
       <c r="D4" t="n">
         <v>1416</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>155</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>17</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +633,23 @@
       <c r="D5" t="n">
         <v>1828</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>176</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>13</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +666,31 @@
       <c r="D6" t="n">
         <v>1728</v>
       </c>
-      <c r="E6" t="n">
-        <v>294</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>170</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="G6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>281</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +707,31 @@
       <c r="D7" t="n">
         <v>1920</v>
       </c>
-      <c r="E7" t="n">
-        <v>294</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>216</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="G7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>199</v>
+      </c>
+      <c r="J7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +748,31 @@
       <c r="D8" t="n">
         <v>1372</v>
       </c>
-      <c r="E8" t="n">
-        <v>206</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>173</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="G8" t="n">
+        <v>17</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>189</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +789,38 @@
       <c r="D9" t="n">
         <v>4296</v>
       </c>
-      <c r="E9" t="n">
-        <v>846</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>283</v>
+        <v>99</v>
+      </c>
+      <c r="G9" t="n">
+        <v>17</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>135</v>
+      </c>
+      <c r="J9" t="n">
+        <v>19</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>264</v>
+      </c>
+      <c r="M9" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +838,31 @@
       <c r="D10" t="n">
         <v>1608</v>
       </c>
-      <c r="E10" t="n">
-        <v>230</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>204</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="G10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>212</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,11 +879,38 @@
       <c r="D11" t="n">
         <v>9064</v>
       </c>
-      <c r="E11" t="n">
-        <v>853</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>593</v>
+        <v>1150</v>
+      </c>
+      <c r="G11" t="n">
+        <v>19</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>815</v>
+      </c>
+      <c r="J11" t="n">
+        <v>18</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>800</v>
+      </c>
+      <c r="M11" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -695,12 +928,15 @@
       <c r="D12" t="n">
         <v>776</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +953,15 @@
       <c r="D13" t="n">
         <v>1624</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +978,23 @@
       <c r="D14" t="n">
         <v>1528</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>228</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>19</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1011,23 @@
       <c r="D15" t="n">
         <v>1860</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>184</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>13</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1044,23 @@
       <c r="D16" t="n">
         <v>1552</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>198</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>14</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1077,31 @@
       <c r="D17" t="n">
         <v>1488</v>
       </c>
-      <c r="E17" t="n">
-        <v>237</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>173</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="G17" t="n">
+        <v>19</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>154</v>
+      </c>
+      <c r="J17" t="n">
+        <v>19</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
